--- a/Simulation_Results.xlsx
+++ b/Simulation_Results.xlsx
@@ -454,7 +454,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I2" t="str">
-        <v>REM A01 | Celdas (A03!L20 + A03!M20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (O36:O37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (L20 + M20) debe ser igual a | celda (O36:O37)</v>
       </c>
     </row>
     <row r="3">
@@ -483,7 +483,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I3" t="str">
-        <v>REM A01 | Celdas (A03!L20 + A03!M20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (O36:O37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (L20 + M20) debe ser igual a | celda (O36:O37)</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I4" t="str">
-        <v>REM A01 | Celdas (A03!L20 + A03!M20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (O36:O37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (L20 + M20) debe ser igual a | celda (O36:O37)</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I5" t="str">
-        <v>REM A01 | Celdas (A03!L20 + A03!M20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (O36:O37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (L20 + M20) debe ser igual a | celda (O36:O37)</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I6" t="str">
-        <v>REM A01 | Celdas (A03!L20 + A03!M20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (O36:O37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (L20 + M20) debe ser igual a | celda (O36:O37)</v>
       </c>
     </row>
     <row r="7">
@@ -599,7 +599,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I7" t="str">
-        <v>REM A01 | Celdas (A03!L20 + A03!M20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (O36:O37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (L20 + M20) debe ser igual a | celda (O36:O37)</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I8" t="str">
-        <v>REM A01 | Celdas (A03!N20 + A03!O20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (A01!P36 + A01!P37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (N20 + O20) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (P36 + P37)</v>
       </c>
     </row>
     <row r="9">
@@ -657,7 +657,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I9" t="str">
-        <v>REM A01 | Celdas (A03!N20 + A03!O20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (A01!P36 + A01!P37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (N20 + O20) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (P36 + P37)</v>
       </c>
     </row>
     <row r="10">
@@ -686,7 +686,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I10" t="str">
-        <v>REM A01 | Celdas (A03!N20 + A03!O20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (A01!P36 + A01!P37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (N20 + O20) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (P36 + P37)</v>
       </c>
     </row>
     <row r="11">
@@ -715,7 +715,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I11" t="str">
-        <v>REM A01 | Celdas (A03!N20 + A03!O20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (A01!P36 + A01!P37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (N20 + O20) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (P36 + P37)</v>
       </c>
     </row>
     <row r="12">
@@ -744,7 +744,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I12" t="str">
-        <v>REM A01 | Celdas (A03!N20 + A03!O20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (A01!P36 + A01!P37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (N20 + O20) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (P36 + P37)</v>
       </c>
     </row>
     <row r="13">
@@ -773,7 +773,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I13" t="str">
-        <v>REM A01 | Celdas (A03!N20 + A03!O20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (A01!P36 + A01!P37)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (N20 + O20) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (P36 + P37)</v>
       </c>
     </row>
     <row r="14">
@@ -802,7 +802,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I14" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (F11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="15">
@@ -831,7 +831,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I15" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (F11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="16">
@@ -860,7 +860,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I16" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (F11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="17">
@@ -889,7 +889,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I17" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (F11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="18">
@@ -918,7 +918,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I18" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (F11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I19" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (F11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="20">
@@ -976,7 +976,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I20" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (F12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="21">
@@ -1005,7 +1005,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I21" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (F12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="22">
@@ -1034,7 +1034,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I22" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (F12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="23">
@@ -1063,7 +1063,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I23" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (F12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="24">
@@ -1092,7 +1092,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I24" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (F12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="25">
@@ -1121,7 +1121,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I25" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (F12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (F12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="26">
@@ -1150,7 +1150,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I26" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (M11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="27">
@@ -1179,7 +1179,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I27" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (M11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="28">
@@ -1208,7 +1208,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I28" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (M11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="29">
@@ -1237,7 +1237,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I29" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (M11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="30">
@@ -1266,7 +1266,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I30" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (M11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="31">
@@ -1295,7 +1295,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I31" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (M11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="32">
@@ -1324,7 +1324,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I32" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (M12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="33">
@@ -1353,7 +1353,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I33" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (M12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="34">
@@ -1382,7 +1382,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I34" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (M12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="35">
@@ -1411,7 +1411,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I35" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (M12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="36">
@@ -1440,7 +1440,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I36" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (M12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="37">
@@ -1469,7 +1469,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I37" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (M12) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (M12) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="38">
@@ -1498,7 +1498,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I38" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (N11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="39">
@@ -1527,7 +1527,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I39" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (N11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="40">
@@ -1556,7 +1556,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I40" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (N11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="41">
@@ -1585,7 +1585,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I41" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (N11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="42">
@@ -1614,7 +1614,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I42" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (N11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="43">
@@ -1643,7 +1643,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I43" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Médico/a' (N11) es distinto de 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N11) debe ser igual a | celda (0)</v>
       </c>
     </row>
     <row r="44">
@@ -1672,7 +1672,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I44" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (N12) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="45">
@@ -1701,7 +1701,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I45" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (N12) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="46">
@@ -1730,7 +1730,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I46" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (N12) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="47">
@@ -1750,16 +1750,16 @@
         <v>0</v>
       </c>
       <c r="F47" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G47" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H47" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I47" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (N12) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="48">
@@ -1779,16 +1779,16 @@
         <v>10</v>
       </c>
       <c r="F48" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G48" t="str">
         <v>Sí</v>
       </c>
       <c r="H48" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I48" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (N12) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="49">
@@ -1817,7 +1817,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I49" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA PreConcepcional Matrona/ón' (N12) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="50">
@@ -1846,7 +1846,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I50" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Médico/a' (N13) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="51">
@@ -1875,7 +1875,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I51" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Médico/a' (N13) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="52">
@@ -1904,7 +1904,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I52" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Médico/a' (N13) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="53">
@@ -1924,16 +1924,16 @@
         <v>0</v>
       </c>
       <c r="F53" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G53" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H53" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I53" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Médico/a' (N13) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="54">
@@ -1953,16 +1953,16 @@
         <v>10</v>
       </c>
       <c r="F54" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G54" t="str">
         <v>Sí</v>
       </c>
       <c r="H54" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I54" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Médico/a' (N13) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="55">
@@ -1991,7 +1991,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I55" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Médico/a' (N13) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="56">
@@ -2020,7 +2020,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I56" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Matrona/ón' (N14) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="57">
@@ -2049,7 +2049,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I57" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Matrona/ón' (N14) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="58">
@@ -2078,7 +2078,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I58" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Matrona/ón' (N14) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="59">
@@ -2098,16 +2098,16 @@
         <v>0</v>
       </c>
       <c r="F59" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G59" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H59" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I59" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Matrona/ón' (N14) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="60">
@@ -2127,16 +2127,16 @@
         <v>10</v>
       </c>
       <c r="F60" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G60" t="str">
         <v>Sí</v>
       </c>
       <c r="H60" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I60" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Matrona/ón' (N14) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="61">
@@ -2165,7 +2165,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I61" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Prenatal Matrona/ón' (N14) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="62">
@@ -2194,7 +2194,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I62" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Médico/a' (N15) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N15) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="63">
@@ -2223,7 +2223,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I63" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Médico/a' (N15) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N15) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="64">
@@ -2252,7 +2252,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I64" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Médico/a' (N15) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N15) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="65">
@@ -2272,16 +2272,16 @@
         <v>0</v>
       </c>
       <c r="F65" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G65" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H65" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I65" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Médico/a' (N15) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N15) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="66">
@@ -2301,16 +2301,16 @@
         <v>10</v>
       </c>
       <c r="F66" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G66" t="str">
         <v>Sí</v>
       </c>
       <c r="H66" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I66" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Médico/a' (N15) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N15) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="67">
@@ -2339,7 +2339,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I67" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Médico/a' (N15) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N15) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="68">
@@ -2368,7 +2368,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I68" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Matrona/ón' (N16) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N16) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="69">
@@ -2397,7 +2397,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I69" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Matrona/ón' (N16) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N16) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="70">
@@ -2426,7 +2426,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I70" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Matrona/ón' (N16) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N16) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="71">
@@ -2446,16 +2446,16 @@
         <v>0</v>
       </c>
       <c r="F71" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G71" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H71" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I71" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Matrona/ón' (N16) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N16) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="72">
@@ -2475,16 +2475,16 @@
         <v>10</v>
       </c>
       <c r="F72" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G72" t="str">
         <v>Sí</v>
       </c>
       <c r="H72" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I72" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Matrona/ón' (N16) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N16) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="73">
@@ -2513,7 +2513,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I73" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA Post Parto Matrona/ón' (N16) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (N16) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="74">
@@ -2542,7 +2542,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I74" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (O31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="75">
@@ -2571,7 +2571,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I75" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (O31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="76">
@@ -2600,7 +2600,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I76" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (O31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="77">
@@ -2620,16 +2620,16 @@
         <v>0</v>
       </c>
       <c r="F77" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G77" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H77" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I77" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (O31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="78">
@@ -2649,16 +2649,16 @@
         <v>10</v>
       </c>
       <c r="F78" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G78" t="str">
         <v>Sí</v>
       </c>
       <c r="H78" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I78" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (O31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="79">
@@ -2687,7 +2687,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I79" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (O31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="80">
@@ -2716,7 +2716,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I80" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (O32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="81">
@@ -2745,7 +2745,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I81" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (O32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="82">
@@ -2774,7 +2774,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I82" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (O32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="83">
@@ -2794,16 +2794,16 @@
         <v>0</v>
       </c>
       <c r="F83" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G83" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H83" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I83" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (O32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="84">
@@ -2823,16 +2823,16 @@
         <v>10</v>
       </c>
       <c r="F84" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G84" t="str">
         <v>Sí</v>
       </c>
       <c r="H84" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I84" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (O32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="85">
@@ -2861,7 +2861,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I85" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (O32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (O32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="86">
@@ -2890,7 +2890,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I86" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (P31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="87">
@@ -2919,7 +2919,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I87" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (P31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="88">
@@ -2948,7 +2948,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I88" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (P31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="89">
@@ -2968,16 +2968,16 @@
         <v>0</v>
       </c>
       <c r="F89" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G89" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H89" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I89" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (P31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="90">
@@ -2997,16 +2997,16 @@
         <v>10</v>
       </c>
       <c r="F90" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G90" t="str">
         <v>Sí</v>
       </c>
       <c r="H90" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I90" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (P31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="91">
@@ -3035,7 +3035,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I91" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (P31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="92">
@@ -3064,7 +3064,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I92" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (P32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="93">
@@ -3093,7 +3093,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I93" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (P32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="94">
@@ -3122,7 +3122,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I94" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (P32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="95">
@@ -3142,16 +3142,16 @@
         <v>0</v>
       </c>
       <c r="F95" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G95" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H95" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I95" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (P32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="96">
@@ -3171,16 +3171,16 @@
         <v>10</v>
       </c>
       <c r="F96" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G96" t="str">
         <v>Sí</v>
       </c>
       <c r="H96" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I96" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (P32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="97">
@@ -3209,7 +3209,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I97" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (P32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (P32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="98">
@@ -3238,7 +3238,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I98" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (Q31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="99">
@@ -3267,7 +3267,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I99" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (Q31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="100">
@@ -3296,7 +3296,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I100" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (Q31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="101">
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="F101" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G101" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H101" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I101" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (Q31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="102">
@@ -3345,16 +3345,16 @@
         <v>10</v>
       </c>
       <c r="F102" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G102" t="str">
         <v>Sí</v>
       </c>
       <c r="H102" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I102" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (Q31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="103">
@@ -3383,7 +3383,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I103" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (Q31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="104">
@@ -3412,7 +3412,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I104" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (Q32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="105">
@@ -3441,7 +3441,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I105" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (Q32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="106">
@@ -3470,7 +3470,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I106" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (Q32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="107">
@@ -3490,16 +3490,16 @@
         <v>0</v>
       </c>
       <c r="F107" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G107" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H107" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I107" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (Q32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="108">
@@ -3519,16 +3519,16 @@
         <v>10</v>
       </c>
       <c r="F108" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G108" t="str">
         <v>Sí</v>
       </c>
       <c r="H108" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I108" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (Q32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="109">
@@ -3557,7 +3557,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I109" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (Q32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (Q32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="110">
@@ -3586,7 +3586,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I110" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (R31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="111">
@@ -3615,7 +3615,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I111" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (R31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="112">
@@ -3644,7 +3644,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I112" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (R31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="113">
@@ -3664,16 +3664,16 @@
         <v>0</v>
       </c>
       <c r="F113" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G113" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H113" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I113" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (R31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="114">
@@ -3693,16 +3693,16 @@
         <v>10</v>
       </c>
       <c r="F114" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G114" t="str">
         <v>Sí</v>
       </c>
       <c r="H114" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I114" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (R31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="115">
@@ -3731,7 +3731,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I115" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (R31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="116">
@@ -3760,7 +3760,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I116" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (R32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="117">
@@ -3789,7 +3789,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I117" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (R32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="118">
@@ -3818,7 +3818,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I118" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (R32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="119">
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="F119" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G119" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H119" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I119" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (R32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="120">
@@ -3867,16 +3867,16 @@
         <v>10</v>
       </c>
       <c r="F120" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G120" t="str">
         <v>Sí</v>
       </c>
       <c r="H120" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I120" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (R32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="121">
@@ -3905,7 +3905,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I121" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (R32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (R32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="122">
@@ -3934,7 +3934,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I122" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (S31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="123">
@@ -3963,7 +3963,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I123" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (S31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="124">
@@ -3992,7 +3992,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I124" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (S31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="125">
@@ -4012,16 +4012,16 @@
         <v>0</v>
       </c>
       <c r="F125" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G125" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H125" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I125" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (S31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="126">
@@ -4041,16 +4041,16 @@
         <v>10</v>
       </c>
       <c r="F126" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G126" t="str">
         <v>Sí</v>
       </c>
       <c r="H126" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I126" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (S31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="127">
@@ -4079,7 +4079,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I127" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (S31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="128">
@@ -4108,7 +4108,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I128" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (S32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="129">
@@ -4137,7 +4137,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I129" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (S32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="130">
@@ -4166,7 +4166,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I130" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (S32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="131">
@@ -4186,16 +4186,16 @@
         <v>0</v>
       </c>
       <c r="F131" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G131" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H131" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I131" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (S32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="132">
@@ -4215,16 +4215,16 @@
         <v>10</v>
       </c>
       <c r="F132" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G132" t="str">
         <v>Sí</v>
       </c>
       <c r="H132" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I132" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (S32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="133">
@@ -4253,7 +4253,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I133" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (S32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (S32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="134">
@@ -4282,7 +4282,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I134" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (T31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="135">
@@ -4311,7 +4311,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I135" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (T31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="136">
@@ -4340,7 +4340,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I136" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (T31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="137">
@@ -4360,16 +4360,16 @@
         <v>0</v>
       </c>
       <c r="F137" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G137" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H137" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I137" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (T31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="138">
@@ -4389,16 +4389,16 @@
         <v>10</v>
       </c>
       <c r="F138" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G138" t="str">
         <v>Sí</v>
       </c>
       <c r="H138" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I138" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (T31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="139">
@@ -4427,7 +4427,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I139" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Médico/a' (T31) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T31) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="140">
@@ -4456,7 +4456,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I140" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (T32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="141">
@@ -4485,7 +4485,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I141" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (T32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="142">
@@ -4514,7 +4514,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I142" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (T32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="143">
@@ -4534,16 +4534,16 @@
         <v>0</v>
       </c>
       <c r="F143" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G143" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H143" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I143" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (T32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="144">
@@ -4563,16 +4563,16 @@
         <v>10</v>
       </c>
       <c r="F144" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G144" t="str">
         <v>Sí</v>
       </c>
       <c r="H144" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I144" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (T32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="145">
@@ -4601,7 +4601,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I145" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | La prestación 'Matrona/ón' (T32) es igual a 0</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (T32) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="146">
@@ -4630,7 +4630,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I146" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | SECCIÓN E: INGRESOS A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (A05!C89)</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (C89)</v>
       </c>
     </row>
     <row r="147">
@@ -4659,7 +4659,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I147" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | SECCIÓN E: INGRESOS A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (A05!C89)</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (C89)</v>
       </c>
     </row>
     <row r="148">
@@ -4688,7 +4688,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I148" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | SECCIÓN E: INGRESOS A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (A05!C89)</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (C89)</v>
       </c>
     </row>
     <row r="149">
@@ -4717,7 +4717,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I149" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | SECCIÓN E: INGRESOS A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (A05!C89)</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (C89)</v>
       </c>
     </row>
     <row r="150">
@@ -4746,7 +4746,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I150" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | SECCIÓN E: INGRESOS A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (A05!C89)</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (C89)</v>
       </c>
     </row>
     <row r="151">
@@ -4775,7 +4775,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I151" t="str">
-        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | SECCIÓN E: INGRESOS A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (A05!C89)</v>
+        <v>REM A01 | SECCIÓN A: CONTROLES DE SALUD SEXUAL Y REPRODUCTIVA | Celdas (SUM(C19:C26, F36:F38)) debe ser igual a | REM A05 | SECCIÓN E:  INGRESOS  A CONTROL DE SALUD DE RECIÉN NACIDOS | celda (C89)</v>
       </c>
     </row>
     <row r="152">
@@ -4804,7 +4804,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I152" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | La prestación 'Médico/a' (F36) es igual a 0</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | Celdas (F36) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="153">
@@ -4833,7 +4833,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I153" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | La prestación 'Médico/a' (F36) es igual a 0</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | Celdas (F36) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="154">
@@ -4862,7 +4862,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I154" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | La prestación 'Médico/a' (F36) es igual a 0</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | Celdas (F36) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="155">
@@ -4882,16 +4882,16 @@
         <v>0</v>
       </c>
       <c r="F155" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G155" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H155" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I155" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | La prestación 'Médico/a' (F36) es igual a 0</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | Celdas (F36) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="156">
@@ -4911,16 +4911,16 @@
         <v>10</v>
       </c>
       <c r="F156" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G156" t="str">
         <v>Sí</v>
       </c>
       <c r="H156" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I156" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | La prestación 'Médico/a' (F36) es igual a 0</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | Celdas (F36) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="157">
@@ -4949,7 +4949,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I157" t="str">
-        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | La prestación 'Médico/a' (F36) es igual a 0</v>
+        <v>REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | Celdas (F36) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="158">
@@ -5326,7 +5326,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I170" t="str">
-        <v>REM A02 | Celdas (A03!C108 + A03!C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108 + C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
       </c>
     </row>
     <row r="171">
@@ -5355,7 +5355,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I171" t="str">
-        <v>REM A02 | Celdas (A03!C108 + A03!C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108 + C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
       </c>
     </row>
     <row r="172">
@@ -5384,7 +5384,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I172" t="str">
-        <v>REM A02 | Celdas (A03!C108 + A03!C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108 + C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
       </c>
     </row>
     <row r="173">
@@ -5413,7 +5413,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I173" t="str">
-        <v>REM A02 | Celdas (A03!C108 + A03!C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108 + C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
       </c>
     </row>
     <row r="174">
@@ -5442,7 +5442,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I174" t="str">
-        <v>REM A02 | Celdas (A03!C108 + A03!C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108 + C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
       </c>
     </row>
     <row r="175">
@@ -5471,7 +5471,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I175" t="str">
-        <v>REM A02 | Celdas (A03!C108 + A03!C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108 + C110) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (B11)</v>
       </c>
     </row>
     <row r="176">
@@ -5500,7 +5500,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I176" t="str">
-        <v>REM A02 | Celdas (A03!C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
       </c>
     </row>
     <row r="177">
@@ -5529,7 +5529,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I177" t="str">
-        <v>REM A02 | Celdas (A03!C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
       </c>
     </row>
     <row r="178">
@@ -5558,7 +5558,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I178" t="str">
-        <v>REM A02 | Celdas (A03!C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
       </c>
     </row>
     <row r="179">
@@ -5587,7 +5587,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I179" t="str">
-        <v>REM A02 | Celdas (A03!C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
       </c>
     </row>
     <row r="180">
@@ -5616,7 +5616,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I180" t="str">
-        <v>REM A02 | Celdas (A03!C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
       </c>
     </row>
     <row r="181">
@@ -5645,7 +5645,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I181" t="str">
-        <v>REM A02 | Celdas (A03!C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C113) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (E11 + F11)</v>
       </c>
     </row>
     <row r="182">
@@ -6022,7 +6022,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I194" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | celda (C214+C215)</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | celda (C214+C215)</v>
       </c>
     </row>
     <row r="195">
@@ -6051,7 +6051,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I195" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | celda (C214+C215)</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | celda (C214+C215)</v>
       </c>
     </row>
     <row r="196">
@@ -6080,7 +6080,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I196" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | celda (C214+C215)</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | celda (C214+C215)</v>
       </c>
     </row>
     <row r="197">
@@ -6109,7 +6109,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I197" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | celda (C214+C215)</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | celda (C214+C215)</v>
       </c>
     </row>
     <row r="198">
@@ -6138,7 +6138,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I198" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | celda (C214+C215)</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | celda (C214+C215)</v>
       </c>
     </row>
     <row r="199">
@@ -6167,7 +6167,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I199" t="str">
-        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | celda (C214+C215)</v>
+        <v>REM A03 | SECCION E: APLICACIÓN DE PAUTA DETECCIÓN DE FACTORES DE RIESGO BIOPSICOSOCIAL INFANTIL | Celdas (C213) debe ser igual a | celda (C214+C215)</v>
       </c>
     </row>
     <row r="200">
@@ -6196,7 +6196,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I200" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (C14:C15)</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | celda (C14:C15)</v>
       </c>
     </row>
     <row r="201">
@@ -6225,7 +6225,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I201" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (C14:C15)</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | celda (C14:C15)</v>
       </c>
     </row>
     <row r="202">
@@ -6254,7 +6254,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I202" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (C14:C15)</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | celda (C14:C15)</v>
       </c>
     </row>
     <row r="203">
@@ -6283,7 +6283,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I203" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (C14:C15)</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | celda (C14:C15)</v>
       </c>
     </row>
     <row r="204">
@@ -6312,7 +6312,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I204" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (C14:C15)</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | celda (C14:C15)</v>
       </c>
     </row>
     <row r="205">
@@ -6341,7 +6341,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I205" t="str">
-        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | celda (C14:C15)</v>
+        <v>REM A03 | SECCIÓN A.1: APLICACIÓN Y RESULTADOS DE PAUTA BREVE | Celdas (C13) debe ser igual a | celda (C14:C15)</v>
       </c>
     </row>
     <row r="206">
@@ -6370,7 +6370,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I206" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (C21:C36)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | celda (C21:C36)</v>
       </c>
     </row>
     <row r="207">
@@ -6399,7 +6399,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I207" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (C21:C36)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | celda (C21:C36)</v>
       </c>
     </row>
     <row r="208">
@@ -6428,7 +6428,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I208" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (C21:C36)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | celda (C21:C36)</v>
       </c>
     </row>
     <row r="209">
@@ -6457,7 +6457,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I209" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (C21:C36)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | celda (C21:C36)</v>
       </c>
     </row>
     <row r="210">
@@ -6486,7 +6486,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I210" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (C21:C36)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | celda (C21:C36)</v>
       </c>
     </row>
     <row r="211">
@@ -6515,7 +6515,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I211" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | celda (C21:C36)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C20) debe ser igual a | celda (C21:C36)</v>
       </c>
     </row>
     <row r="212">
@@ -6544,7 +6544,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I212" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
       </c>
     </row>
     <row r="213">
@@ -6573,7 +6573,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I213" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
       </c>
     </row>
     <row r="214">
@@ -6602,7 +6602,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I214" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
       </c>
     </row>
     <row r="215">
@@ -6631,7 +6631,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I215" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
       </c>
     </row>
     <row r="216">
@@ -6660,7 +6660,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I216" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
       </c>
     </row>
     <row r="217">
@@ -6689,7 +6689,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I217" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C22) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B46)</v>
       </c>
     </row>
     <row r="218">
@@ -6718,7 +6718,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I218" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
       </c>
     </row>
     <row r="219">
@@ -6747,7 +6747,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I219" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
       </c>
     </row>
     <row r="220">
@@ -6776,7 +6776,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I220" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
       </c>
     </row>
     <row r="221">
@@ -6805,7 +6805,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I221" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
       </c>
     </row>
     <row r="222">
@@ -6834,7 +6834,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I222" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
       </c>
     </row>
     <row r="223">
@@ -6863,7 +6863,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I223" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C23) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B47)</v>
       </c>
     </row>
     <row r="224">
@@ -6892,7 +6892,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I224" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
       </c>
     </row>
     <row r="225">
@@ -6921,7 +6921,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I225" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
       </c>
     </row>
     <row r="226">
@@ -6950,7 +6950,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I226" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
       </c>
     </row>
     <row r="227">
@@ -6979,7 +6979,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I227" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
       </c>
     </row>
     <row r="228">
@@ -7008,7 +7008,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I228" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
       </c>
     </row>
     <row r="229">
@@ -7037,7 +7037,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I229" t="str">
-        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
+        <v>REM A03 | SECCIÓN A.2: RESULTADOS DE LA APLICACIÓN DE ESCALA DE EVALUACIÓN DEL DESARROLLO PSICOMOTOR | Celdas (C24) debe ser igual a | SECCIÓN A.3: NIÑOS Y NIÑAS CON REZAGO, DÉFICIT O RIESGO BIOPSICOSOCIAL  DERIVADOS A ALGUNA MODALIDAD DE ESTIMULACIÓN EN LA PRIMERA EVALUACIÓN | celda (B48)</v>
       </c>
     </row>
     <row r="230">
@@ -7066,7 +7066,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I230" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | celda (C55:C57)</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | celda (C55:C57)</v>
       </c>
     </row>
     <row r="231">
@@ -7095,7 +7095,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I231" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | celda (C55:C57)</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | celda (C55:C57)</v>
       </c>
     </row>
     <row r="232">
@@ -7124,7 +7124,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I232" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | celda (C55:C57)</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | celda (C55:C57)</v>
       </c>
     </row>
     <row r="233">
@@ -7153,7 +7153,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I233" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | celda (C55:C57)</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | celda (C55:C57)</v>
       </c>
     </row>
     <row r="234">
@@ -7182,7 +7182,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I234" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | celda (C55:C57)</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | celda (C55:C57)</v>
       </c>
     </row>
     <row r="235">
@@ -7211,7 +7211,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I235" t="str">
-        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | celda (C55:C57)</v>
+        <v>REM A03 | SECCIÓN A.4: RESULTADOS DE LA APLICACIÓN DE PROTOCOLO NEUROSENSORIAL | Celdas (C54) debe ser igual a | celda (C55:C57)</v>
       </c>
     </row>
     <row r="236">
@@ -7240,7 +7240,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I236" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | celda (C67)</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | celda (C67)</v>
       </c>
     </row>
     <row r="237">
@@ -7269,7 +7269,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I237" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | celda (C67)</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | celda (C67)</v>
       </c>
     </row>
     <row r="238">
@@ -7298,7 +7298,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I238" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | celda (C67)</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | celda (C67)</v>
       </c>
     </row>
     <row r="239">
@@ -7327,7 +7327,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I239" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | celda (C67)</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | celda (C67)</v>
       </c>
     </row>
     <row r="240">
@@ -7356,7 +7356,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I240" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | celda (C67)</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | celda (C67)</v>
       </c>
     </row>
     <row r="241">
@@ -7385,7 +7385,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I241" t="str">
-        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | celda (C67)</v>
+        <v>REM A03 | SECCIÓN A.5: TIPO DE ALIMENTACIÓN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C61:C66) debe ser igual a | celda (C67)</v>
       </c>
     </row>
     <row r="242">
@@ -7414,7 +7414,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I242" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (A05!C11)</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (C11)</v>
       </c>
     </row>
     <row r="243">
@@ -7443,7 +7443,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I243" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (A05!C11)</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (C11)</v>
       </c>
     </row>
     <row r="244">
@@ -7472,7 +7472,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I244" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (A05!C11)</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (C11)</v>
       </c>
     </row>
     <row r="245">
@@ -7501,7 +7501,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I245" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (A05!C11)</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (C11)</v>
       </c>
     </row>
     <row r="246">
@@ -7530,7 +7530,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I246" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (A05!C11)</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (C11)</v>
       </c>
     </row>
     <row r="247">
@@ -7559,7 +7559,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I247" t="str">
-        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (A05!C11)</v>
+        <v>REM A03 | SECCIÓN B.2: APLICACIÓN DE ESCALA SEGÚN EVALUACIÓN DE RIESGO PSICOSOCIAL ABREVIADA A GESTANTES | Celdas (B86) debe ser igual a | REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | celda (C11)</v>
       </c>
     </row>
     <row r="248">
@@ -7588,7 +7588,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I248" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(H36:H37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (H36:H37)</v>
       </c>
     </row>
     <row r="249">
@@ -7617,7 +7617,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I249" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(H36:H37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (H36:H37)</v>
       </c>
     </row>
     <row r="250">
@@ -7646,7 +7646,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I250" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(H36:H37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (H36:H37)</v>
       </c>
     </row>
     <row r="251">
@@ -7675,7 +7675,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I251" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(H36:H37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (H36:H37)</v>
       </c>
     </row>
     <row r="252">
@@ -7704,7 +7704,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I252" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(H36:H37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (H36:H37)</v>
       </c>
     </row>
     <row r="253">
@@ -7733,7 +7733,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I253" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(H36:H37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C92) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (H36:H37)</v>
       </c>
     </row>
     <row r="254">
@@ -7762,7 +7762,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I254" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(L36:L37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (L36:L37)</v>
       </c>
     </row>
     <row r="255">
@@ -7791,7 +7791,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I255" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(L36:L37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (L36:L37)</v>
       </c>
     </row>
     <row r="256">
@@ -7820,7 +7820,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I256" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(L36:L37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (L36:L37)</v>
       </c>
     </row>
     <row r="257">
@@ -7849,7 +7849,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I257" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(L36:L37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (L36:L37)</v>
       </c>
     </row>
     <row r="258">
@@ -7878,7 +7878,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I258" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(L36:L37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (L36:L37)</v>
       </c>
     </row>
     <row r="259">
@@ -7907,7 +7907,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I259" t="str">
-        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(L36:L37))</v>
+        <v>REM A03 | SECCIÓN B.3: APLICACIÓN DE ESCALA DE EDIMBURGO A GESTANTES Y MUJERES POST PARTO | Celdas (C93) debe ser menor o igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (L36:L37)</v>
       </c>
     </row>
     <row r="260">
@@ -7936,7 +7936,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I260" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(T36:U38))</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (T36:U38)</v>
       </c>
     </row>
     <row r="261">
@@ -7965,7 +7965,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I261" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(T36:U38))</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (T36:U38)</v>
       </c>
     </row>
     <row r="262">
@@ -7994,7 +7994,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I262" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(T36:U38))</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (T36:U38)</v>
       </c>
     </row>
     <row r="263">
@@ -8023,7 +8023,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I263" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(T36:U38))</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (T36:U38)</v>
       </c>
     </row>
     <row r="264">
@@ -8052,7 +8052,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I264" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(T36:U38))</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (T36:U38)</v>
       </c>
     </row>
     <row r="265">
@@ -8081,7 +8081,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I265" t="str">
-        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (A01!(T36:U38))</v>
+        <v>REM A03 | SECCIÓN C: RESULTADOS DE LA EVALUACIÓN DEL ESTADO NUTRICIONAL DEL ADOLESCENTE CON CONTROL SALUD INTEGRAL | Celdas (C97) debe ser igual a | REM A01 | SECCIÓN B: CONTROLES DE SALUD SEGÚN CICLO VITAL | celda (T36:U38)</v>
       </c>
     </row>
     <row r="266">
@@ -8110,7 +8110,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I266" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | celda (C115:C117)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | celda (C115:C117)</v>
       </c>
     </row>
     <row r="267">
@@ -8139,7 +8139,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I267" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | celda (C115:C117)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | celda (C115:C117)</v>
       </c>
     </row>
     <row r="268">
@@ -8168,7 +8168,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I268" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | celda (C115:C117)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | celda (C115:C117)</v>
       </c>
     </row>
     <row r="269">
@@ -8197,7 +8197,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I269" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | celda (C115:C117)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | celda (C115:C117)</v>
       </c>
     </row>
     <row r="270">
@@ -8226,7 +8226,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I270" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | celda (C115:C117)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | celda (C115:C117)</v>
       </c>
     </row>
     <row r="271">
@@ -8255,7 +8255,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I271" t="str">
-        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE ALCOHOL, TABACO Y OTRAS DROGAS | celda (C115:C117)</v>
+        <v>REM A03 | SECCIÓN D.1: APLICACIÓN DE TAMIZAJE PARA EVALUAR EL NIVEL DE RIESGO DE CONSUMO DE  ALCOHOL, TABACO Y OTRAS DROGAS | Celdas (C108:C114) debe ser igual a | celda (C115:C117)</v>
       </c>
     </row>
     <row r="272">
@@ -8458,7 +8458,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I278" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E114+F114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | celda (E114+F114)</v>
       </c>
     </row>
     <row r="279">
@@ -8487,7 +8487,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I279" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E114+F114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | celda (E114+F114)</v>
       </c>
     </row>
     <row r="280">
@@ -8516,7 +8516,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I280" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E114+F114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | celda (E114+F114)</v>
       </c>
     </row>
     <row r="281">
@@ -8545,7 +8545,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I281" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E114+F114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | celda (E114+F114)</v>
       </c>
     </row>
     <row r="282">
@@ -8574,7 +8574,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I282" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E114+F114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | celda (E114+F114)</v>
       </c>
     </row>
     <row r="283">
@@ -8603,7 +8603,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I283" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E114+F114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C114+D114) debe ser igual a | celda (E114+F114)</v>
       </c>
     </row>
     <row r="284">
@@ -8632,7 +8632,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I284" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E115+F115)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | celda (E115+F115)</v>
       </c>
     </row>
     <row r="285">
@@ -8661,7 +8661,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I285" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E115+F115)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | celda (E115+F115)</v>
       </c>
     </row>
     <row r="286">
@@ -8690,7 +8690,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I286" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E115+F115)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | celda (E115+F115)</v>
       </c>
     </row>
     <row r="287">
@@ -8719,7 +8719,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I287" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E115+F115)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | celda (E115+F115)</v>
       </c>
     </row>
     <row r="288">
@@ -8748,7 +8748,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I288" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E115+F115)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | celda (E115+F115)</v>
       </c>
     </row>
     <row r="289">
@@ -8777,7 +8777,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I289" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E115+F115)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C115+D115) debe ser igual a | celda (E115+F115)</v>
       </c>
     </row>
     <row r="290">
@@ -8806,7 +8806,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I290" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E116+F116)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | celda (E116+F116)</v>
       </c>
     </row>
     <row r="291">
@@ -8835,7 +8835,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I291" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E116+F116)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | celda (E116+F116)</v>
       </c>
     </row>
     <row r="292">
@@ -8864,7 +8864,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I292" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E116+F116)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | celda (E116+F116)</v>
       </c>
     </row>
     <row r="293">
@@ -8893,7 +8893,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I293" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E116+F116)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | celda (E116+F116)</v>
       </c>
     </row>
     <row r="294">
@@ -8922,7 +8922,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I294" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E116+F116)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | celda (E116+F116)</v>
       </c>
     </row>
     <row r="295">
@@ -8951,7 +8951,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I295" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (E116+F116)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (C116+D116) debe ser igual a | celda (E116+F116)</v>
       </c>
     </row>
     <row r="296">
@@ -8980,7 +8980,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I296" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (L114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | celda (L114)</v>
       </c>
     </row>
     <row r="297">
@@ -9009,7 +9009,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I297" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (L114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | celda (L114)</v>
       </c>
     </row>
     <row r="298">
@@ -9038,7 +9038,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I298" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (L114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | celda (L114)</v>
       </c>
     </row>
     <row r="299">
@@ -9067,7 +9067,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I299" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (L114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | celda (L114)</v>
       </c>
     </row>
     <row r="300">
@@ -9096,7 +9096,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I300" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (L114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | celda (L114)</v>
       </c>
     </row>
     <row r="301">
@@ -9125,7 +9125,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I301" t="str">
-        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | celda (L114)</v>
+        <v>REM A04 | SECCIÓN I.1 : DESPACHO DE RECETAS DE PACIENTES AMBULATORIOS EN ATENCIÓN PRIMARIA | Celdas (M114) debe ser mayor o igual a | celda (L114)</v>
       </c>
     </row>
     <row r="302">
@@ -9154,7 +9154,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I302" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | celda (C146:C149)</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | celda (C146:C149)</v>
       </c>
     </row>
     <row r="303">
@@ -9183,7 +9183,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I303" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | celda (C146:C149)</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | celda (C146:C149)</v>
       </c>
     </row>
     <row r="304">
@@ -9212,7 +9212,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I304" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | celda (C146:C149)</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | celda (C146:C149)</v>
       </c>
     </row>
     <row r="305">
@@ -9241,7 +9241,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I305" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | celda (C146:C149)</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | celda (C146:C149)</v>
       </c>
     </row>
     <row r="306">
@@ -9270,7 +9270,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I306" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | celda (C146:C149)</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | celda (C146:C149)</v>
       </c>
     </row>
     <row r="307">
@@ -9299,7 +9299,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I307" t="str">
-        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | celda (C146:C149)</v>
+        <v>REM A04 | SECCIÓN L: CONSULTA DE LACTANCIA EN NIÑOS Y NIÑAS CONTROLADOS | Celdas (C141:C143) debe ser igual a | celda (C146:C149)</v>
       </c>
     </row>
     <row r="308">
@@ -9328,7 +9328,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I308" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | La prestación 'INGRESOS DE GESTANTES A PROGRAMA PRENATAL Gestantes Ingresadas' (L11:N14) es igual a 0</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | Celdas (L11:N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="309">
@@ -9357,7 +9357,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I309" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | La prestación 'INGRESOS DE GESTANTES A PROGRAMA PRENATAL Gestantes Ingresadas' (L11:N14) es igual a 0</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | Celdas (L11:N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="310">
@@ -9386,7 +9386,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I310" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | La prestación 'INGRESOS DE GESTANTES A PROGRAMA PRENATAL Gestantes Ingresadas' (L11:N14) es igual a 0</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | Celdas (L11:N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="311">
@@ -9406,16 +9406,16 @@
         <v>0</v>
       </c>
       <c r="F311" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G311" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H311" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I311" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | La prestación 'INGRESOS DE GESTANTES A PROGRAMA PRENATAL Gestantes Ingresadas' (L11:N14) es igual a 0</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | Celdas (L11:N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="312">
@@ -9435,16 +9435,16 @@
         <v>10</v>
       </c>
       <c r="F312" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G312" t="str">
         <v>Sí</v>
       </c>
       <c r="H312" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I312" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | La prestación 'INGRESOS DE GESTANTES A PROGRAMA PRENATAL Gestantes Ingresadas' (L11:N14) es igual a 0</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | Celdas (L11:N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="313">
@@ -9473,7 +9473,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I313" t="str">
-        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | La prestación 'INGRESOS DE GESTANTES A PROGRAMA PRENATAL Gestantes Ingresadas' (L11:N14) es igual a 0</v>
+        <v>REM A05 | SECCIÓN A: INGRESOS DE GESTANTES A PROGRAMA PRENATAL | Celdas (L11:N14) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="314">
@@ -9502,7 +9502,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I314" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | celda (C120:C127)</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | celda (C120:C127)</v>
       </c>
     </row>
     <row r="315">
@@ -9531,7 +9531,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I315" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | celda (C120:C127)</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | celda (C120:C127)</v>
       </c>
     </row>
     <row r="316">
@@ -9560,7 +9560,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I316" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | celda (C120:C127)</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | celda (C120:C127)</v>
       </c>
     </row>
     <row r="317">
@@ -9589,7 +9589,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I317" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | celda (C120:C127)</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | celda (C120:C127)</v>
       </c>
     </row>
     <row r="318">
@@ -9618,7 +9618,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I318" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | celda (C120:C127)</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | celda (C120:C127)</v>
       </c>
     </row>
     <row r="319">
@@ -9647,7 +9647,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I319" t="str">
-        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | celda (C120:C127)</v>
+        <v>REM A05 | SECCIÓN H: INGRESOS AL PROGRAMA DE SALUD CARDIOVASCULAR (PSCV) | Celdas (C119) debe ser menor o igual a | celda (C120:C127)</v>
       </c>
     </row>
     <row r="320">
@@ -9850,7 +9850,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I326" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C204)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | celda (C204)</v>
       </c>
     </row>
     <row r="327">
@@ -9879,7 +9879,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I327" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C204)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | celda (C204)</v>
       </c>
     </row>
     <row r="328">
@@ -9908,7 +9908,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I328" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C204)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | celda (C204)</v>
       </c>
     </row>
     <row r="329">
@@ -9937,7 +9937,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I329" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C204)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | celda (C204)</v>
       </c>
     </row>
     <row r="330">
@@ -9966,7 +9966,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I330" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C204)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | celda (C204)</v>
       </c>
     </row>
     <row r="331">
@@ -9995,7 +9995,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I331" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C204)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C193) debe ser igual a | celda (C204)</v>
       </c>
     </row>
     <row r="332">
@@ -10024,7 +10024,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I332" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C205:C241)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | celda (C205:C241)</v>
       </c>
     </row>
     <row r="333">
@@ -10053,7 +10053,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I333" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C205:C241)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | celda (C205:C241)</v>
       </c>
     </row>
     <row r="334">
@@ -10082,7 +10082,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I334" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C205:C241)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | celda (C205:C241)</v>
       </c>
     </row>
     <row r="335">
@@ -10111,7 +10111,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I335" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C205:C241)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | celda (C205:C241)</v>
       </c>
     </row>
     <row r="336">
@@ -10140,7 +10140,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I336" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C205:C241)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | celda (C205:C241)</v>
       </c>
     </row>
     <row r="337">
@@ -10169,7 +10169,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I337" t="str">
-        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | celda (C205:C241)</v>
+        <v>REM A05 | SECCIÓN N: INGRESOS AL PROGRAMA DE SALUD MENTAL EN APS /ESPECIALIDAD | Celdas (C204) debe ser menor o igual a | celda (C205:C241)</v>
       </c>
     </row>
     <row r="338">
@@ -10372,7 +10372,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I344" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | celda (AS13)</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | celda (AS13)</v>
       </c>
     </row>
     <row r="345">
@@ -10401,7 +10401,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I345" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | celda (AS13)</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | celda (AS13)</v>
       </c>
     </row>
     <row r="346">
@@ -10430,7 +10430,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I346" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | celda (AS13)</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | celda (AS13)</v>
       </c>
     </row>
     <row r="347">
@@ -10459,7 +10459,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I347" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | celda (AS13)</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | celda (AS13)</v>
       </c>
     </row>
     <row r="348">
@@ -10488,7 +10488,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I348" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | celda (AS13)</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | celda (AS13)</v>
       </c>
     </row>
     <row r="349">
@@ -10517,7 +10517,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I349" t="str">
-        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | celda (AS13)</v>
+        <v>REM A08 | SECCIÓN A.1: ATENCIONES REALIZADAS EN UNIDADES DE EMERGENCIA HOSPITALARIA (Establecimientos de alta y mediana complejidad) | Celdas (B13) debe ser menor que | celda (AS13)</v>
       </c>
     </row>
     <row r="350">
@@ -10546,7 +10546,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I350" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | La prestación 'C1' (C61:AL66) es igual a 0</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | Celdas (C61:AL66) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="351">
@@ -10575,7 +10575,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I351" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | La prestación 'C1' (C61:AL66) es igual a 0</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | Celdas (C61:AL66) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="352">
@@ -10604,7 +10604,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I352" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | La prestación 'C1' (C61:AL66) es igual a 0</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | Celdas (C61:AL66) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="353">
@@ -10624,16 +10624,16 @@
         <v>0</v>
       </c>
       <c r="F353" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G353" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H353" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I353" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | La prestación 'C1' (C61:AL66) es igual a 0</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | Celdas (C61:AL66) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="354">
@@ -10653,16 +10653,16 @@
         <v>10</v>
       </c>
       <c r="F354" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G354" t="str">
         <v>Sí</v>
       </c>
       <c r="H354" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I354" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | La prestación 'C1' (C61:AL66) es igual a 0</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | Celdas (C61:AL66) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="355">
@@ -10691,7 +10691,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I355" t="str">
-        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | La prestación 'C1' (C61:AL66) es igual a 0</v>
+        <v>REM A08 | SECCIÓN B: CATEGORIZACIÓN DE PACIENTES, PREVIA A LA ATENCIÓN MÉDICA U ODONTOLÓGICA (Establecimientos Alta, Mediana, Baja Complejidad, SAPU, SAR, SUR) | Celdas (C61:AL66) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="356">
@@ -10720,7 +10720,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I356" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | La prestación 'Nº de llamados de urgencia' (C161+D161) es igual a 0</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | Celdas (C161+D161) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="357">
@@ -10749,7 +10749,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I357" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | La prestación 'Nº de llamados de urgencia' (C161+D161) es igual a 0</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | Celdas (C161+D161) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="358">
@@ -10778,7 +10778,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I358" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | La prestación 'Nº de llamados de urgencia' (C161+D161) es igual a 0</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | Celdas (C161+D161) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="359">
@@ -10798,16 +10798,16 @@
         <v>0</v>
       </c>
       <c r="F359" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G359" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H359" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I359" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | La prestación 'Nº de llamados de urgencia' (C161+D161) es igual a 0</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | Celdas (C161+D161) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="360">
@@ -10827,16 +10827,16 @@
         <v>10</v>
       </c>
       <c r="F360" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G360" t="str">
         <v>Sí</v>
       </c>
       <c r="H360" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I360" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | La prestación 'Nº de llamados de urgencia' (C161+D161) es igual a 0</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | Celdas (C161+D161) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="361">
@@ -10865,7 +10865,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I361" t="str">
-        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | La prestación 'Nº de llamados de urgencia' (C161+D161) es igual a 0</v>
+        <v>REM A08 | SECCIÓN J: LLAMADOS DE URGENCIA A CENTRO REGULADOR, CENTRO DE DESPACHO O CENTRO COORDINADOR | Celdas (C161+D161) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="362">
@@ -10894,7 +10894,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I362" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'BASICO' (C171:F171) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C171:F171) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="363">
@@ -10923,7 +10923,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I363" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'BASICO' (C171:F171) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C171:F171) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="364">
@@ -10952,7 +10952,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I364" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'BASICO' (C171:F171) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C171:F171) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="365">
@@ -10972,16 +10972,16 @@
         <v>0</v>
       </c>
       <c r="F365" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G365" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H365" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I365" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'BASICO' (C171:F171) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C171:F171) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="366">
@@ -11001,16 +11001,16 @@
         <v>10</v>
       </c>
       <c r="F366" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G366" t="str">
         <v>Sí</v>
       </c>
       <c r="H366" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I366" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'BASICO' (C171:F171) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C171:F171) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="367">
@@ -11039,7 +11039,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I367" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'BASICO' (C171:F171) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C171:F171) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="368">
@@ -11068,7 +11068,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I368" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'TERRESTRE' (C172:F174) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C172:F174) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="369">
@@ -11097,7 +11097,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I369" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'TERRESTRE' (C172:F174) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C172:F174) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="370">
@@ -11126,7 +11126,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I370" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'TERRESTRE' (C172:F174) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C172:F174) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="371">
@@ -11146,16 +11146,16 @@
         <v>0</v>
       </c>
       <c r="F371" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G371" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H371" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I371" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'TERRESTRE' (C172:F174) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C172:F174) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="372">
@@ -11175,16 +11175,16 @@
         <v>10</v>
       </c>
       <c r="F372" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G372" t="str">
         <v>Sí</v>
       </c>
       <c r="H372" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I372" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'TERRESTRE' (C172:F174) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C172:F174) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="373">
@@ -11213,7 +11213,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I373" t="str">
-        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | La prestación 'TERRESTRE' (C172:F174) es igual a 0</v>
+        <v>REM A08 | SECCIÓN L: TRASLADOS PRIMARIOS A UNIDADES DE URGENCIA (Desde el lugar del evento a unidad de Emergencia) | Celdas (C172:F174) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="374">
@@ -11242,7 +11242,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I374" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | La prestación 'Aéreo' (E178:E183) es igual a 0</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | Celdas (E178:E183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="375">
@@ -11271,7 +11271,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I375" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | La prestación 'Aéreo' (E178:E183) es igual a 0</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | Celdas (E178:E183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="376">
@@ -11300,7 +11300,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I376" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | La prestación 'Aéreo' (E178:E183) es igual a 0</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | Celdas (E178:E183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="377">
@@ -11320,16 +11320,16 @@
         <v>0</v>
       </c>
       <c r="F377" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G377" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H377" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I377" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | La prestación 'Aéreo' (E178:E183) es igual a 0</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | Celdas (E178:E183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="378">
@@ -11349,16 +11349,16 @@
         <v>10</v>
       </c>
       <c r="F378" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G378" t="str">
         <v>Sí</v>
       </c>
       <c r="H378" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I378" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | La prestación 'Aéreo' (E178:E183) es igual a 0</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | Celdas (E178:E183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="379">
@@ -11387,7 +11387,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I379" t="str">
-        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | La prestación 'Aéreo' (E178:E183) es igual a 0</v>
+        <v>REM A08 | SECCIÓN M: TRASLADO SECUNDARIO (Desde un establecimiento a otro) | Celdas (E178:E183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="380">
@@ -11416,7 +11416,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I380" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD | La prestación 'CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD Consulta nueva de Operatoria de alta complejidad' (D16+D17) es igual a 0</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | Celdas (D16+D17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="381">
@@ -11445,7 +11445,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I381" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD | La prestación 'CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD Consulta nueva de Operatoria de alta complejidad' (D16+D17) es igual a 0</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | Celdas (D16+D17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="382">
@@ -11474,7 +11474,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I382" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD | La prestación 'CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD Consulta nueva de Operatoria de alta complejidad' (D16+D17) es igual a 0</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | Celdas (D16+D17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="383">
@@ -11494,16 +11494,16 @@
         <v>0</v>
       </c>
       <c r="F383" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G383" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H383" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I383" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD | La prestación 'CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD Consulta nueva de Operatoria de alta complejidad' (D16+D17) es igual a 0</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | Celdas (D16+D17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="384">
@@ -11523,16 +11523,16 @@
         <v>10</v>
       </c>
       <c r="F384" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G384" t="str">
         <v>Sí</v>
       </c>
       <c r="H384" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I384" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD | La prestación 'CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD Consulta nueva de Operatoria de alta complejidad' (D16+D17) es igual a 0</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | Celdas (D16+D17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="385">
@@ -11561,7 +11561,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I385" t="str">
-        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD | La prestación 'CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN NIVEL PRIMARIO Y SECUNDARIO DE SALUD Consulta nueva de Operatoria de alta complejidad' (D16+D17) es igual a 0</v>
+        <v>REM A09 | SECCIÓN A: CONSULTAS Y CONTROLES DE ODONTOLOGÍA GENERAL EN  NIVEL PRIMARIO Y SECUNDARIO DE SALUD | Celdas (D16+D17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="386">
@@ -11590,7 +11590,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I386" t="str">
-        <v>REM A11 | SECCION A: TRATAMIENTO DE SÍFILIS EN GESTANTES | La prestación 'GESTANTES PRIMER TRIMESTRE EMBARAZO' (B13:C30) es igual a 0</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (B13:C30) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="387">
@@ -11619,7 +11619,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I387" t="str">
-        <v>REM A11 | SECCION A: TRATAMIENTO DE SÍFILIS EN GESTANTES | La prestación 'GESTANTES PRIMER TRIMESTRE EMBARAZO' (B13:C30) es igual a 0</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (B13:C30) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="388">
@@ -11648,7 +11648,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I388" t="str">
-        <v>REM A11 | SECCION A: TRATAMIENTO DE SÍFILIS EN GESTANTES | La prestación 'GESTANTES PRIMER TRIMESTRE EMBARAZO' (B13:C30) es igual a 0</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (B13:C30) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="389">
@@ -11668,16 +11668,16 @@
         <v>0</v>
       </c>
       <c r="F389" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G389" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H389" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I389" t="str">
-        <v>REM A11 | SECCION A: TRATAMIENTO DE SÍFILIS EN GESTANTES | La prestación 'GESTANTES PRIMER TRIMESTRE EMBARAZO' (B13:C30) es igual a 0</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (B13:C30) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="390">
@@ -11697,16 +11697,16 @@
         <v>10</v>
       </c>
       <c r="F390" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G390" t="str">
         <v>Sí</v>
       </c>
       <c r="H390" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I390" t="str">
-        <v>REM A11 | SECCION A: TRATAMIENTO DE SÍFILIS EN GESTANTES | La prestación 'GESTANTES PRIMER TRIMESTRE EMBARAZO' (B13:C30) es igual a 0</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (B13:C30) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="391">
@@ -11735,7 +11735,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I391" t="str">
-        <v>REM A11 | SECCION A: TRATAMIENTO DE SÍFILIS EN GESTANTES | La prestación 'GESTANTES PRIMER TRIMESTRE EMBARAZO' (B13:C30) es igual a 0</v>
+        <v>REM A11 | SECCIÓN A.1: EXAMEN VDRL POR GRUPO DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (B13:C30) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="392">
@@ -11764,7 +11764,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I392" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C144:P148) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C144:P148) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="393">
@@ -11793,7 +11793,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I393" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C144:P148) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C144:P148) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="394">
@@ -11822,7 +11822,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I394" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C144:P148) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C144:P148) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="395">
@@ -11842,16 +11842,16 @@
         <v>0</v>
       </c>
       <c r="F395" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G395" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H395" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I395" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C144:P148) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C144:P148) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="396">
@@ -11871,16 +11871,16 @@
         <v>10</v>
       </c>
       <c r="F396" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G396" t="str">
         <v>Sí</v>
       </c>
       <c r="H396" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I396" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C144:P148) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C144:P148) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="397">
@@ -11909,7 +11909,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I397" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C144:P148) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.1: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C144:P148) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="398">
@@ -11938,7 +11938,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I398" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C152:P156) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | Celdas (C152:P156) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="399">
@@ -11967,7 +11967,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I399" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C152:P156) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | Celdas (C152:P156) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="400">
@@ -11996,7 +11996,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I400" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C152:P156) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | Celdas (C152:P156) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="401">
@@ -12025,7 +12025,7 @@
         <v>Omitida: v1 es 0</v>
       </c>
       <c r="I401" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C152:P156) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | Celdas (C152:P156) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="402">
@@ -12054,7 +12054,7 @@
         <v>Omitida: v1 es 0</v>
       </c>
       <c r="I402" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C152:P156) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | Celdas (C152:P156) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="403">
@@ -12083,7 +12083,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I403" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'USUARIOS' (C152:P156) es igual a 0</v>
+        <v>REM A11 | SECCIÓN B.2: EXÁMENES SEGÚN GRUPOS DE USUARIOS POR CONDICIÓN DE HEPATITIS B, HEPATITIS C, CHAGAS, HTLV 1 Y SIFILIS (USO EXCLUSIVO DE ESTABLECIMIENTOS QUE COMPRAN SERVICIO) | Celdas (C152:P156) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="404">
@@ -12112,7 +12112,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I404" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'GESTANTES PRIMER EXAMEN' (C161:D183) es igual a 0</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C161:D183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="405">
@@ -12141,7 +12141,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I405" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'GESTANTES PRIMER EXAMEN' (C161:D183) es igual a 0</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C161:D183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="406">
@@ -12170,7 +12170,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I406" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'GESTANTES PRIMER EXAMEN' (C161:D183) es igual a 0</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C161:D183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="407">
@@ -12190,16 +12190,16 @@
         <v>0</v>
       </c>
       <c r="F407" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G407" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H407" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I407" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'GESTANTES PRIMER EXAMEN' (C161:D183) es igual a 0</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C161:D183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="408">
@@ -12219,16 +12219,16 @@
         <v>10</v>
       </c>
       <c r="F408" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G408" t="str">
         <v>Sí</v>
       </c>
       <c r="H408" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I408" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'GESTANTES PRIMER EXAMEN' (C161:D183) es igual a 0</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C161:D183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="409">
@@ -12257,7 +12257,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I409" t="str">
-        <v>REM A11 | SECCION N: TRATAMIENTOS FAMACOLÓGICOS | La prestación 'GESTANTES PRIMER EXAMEN' (C161:D183) es igual a 0</v>
+        <v>REM A11 | SECCIÓN C.1: EXÁMENES  DE  VIH POR GRUPOS DE USUARIOS (USO EXCLUSIVO DE ESTABLECIMIENTOS CON LABORATORIO QUE PROCESAN) | Celdas (C161:D183) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="410">
@@ -12286,7 +12286,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I410" t="str">
-        <v>REM A19a | ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
       </c>
     </row>
     <row r="411">
@@ -12315,7 +12315,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I411" t="str">
-        <v>REM A19a | ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
       </c>
     </row>
     <row r="412">
@@ -12344,7 +12344,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I412" t="str">
-        <v>REM A19a | ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
       </c>
     </row>
     <row r="413">
@@ -12373,7 +12373,7 @@
         <v>Omitida: v1 es 0</v>
       </c>
       <c r="I413" t="str">
-        <v>REM A19a | ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
       </c>
     </row>
     <row r="414">
@@ -12402,7 +12402,7 @@
         <v>Omitida: v1 es 0</v>
       </c>
       <c r="I414" t="str">
-        <v>REM A19a | ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
       </c>
     </row>
     <row r="415">
@@ -12431,7 +12431,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I415" t="str">
-        <v>REM A19a | ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
+        <v>REM A19a | SECCIÓN B.1: ACTIVIDADES DE PROMOCIÓN SEGÚN ESTRATEGIAS Y CONDICIONANTES ABORDADAS Y NÚMERO DE PARTICIPANTES | Celdas (C129:C148) debe ser menor o igual a | celda (O129:O148)</v>
       </c>
     </row>
     <row r="416">
@@ -12460,7 +12460,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I416" t="str">
-        <v>REM A19b | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
       </c>
     </row>
     <row r="417">
@@ -12489,7 +12489,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I417" t="str">
-        <v>REM A19b | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
       </c>
     </row>
     <row r="418">
@@ -12518,7 +12518,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I418" t="str">
-        <v>REM A19b | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
       </c>
     </row>
     <row r="419">
@@ -12547,7 +12547,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I419" t="str">
-        <v>REM A19b | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
       </c>
     </row>
     <row r="420">
@@ -12576,7 +12576,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I420" t="str">
-        <v>REM A19b | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
       </c>
     </row>
     <row r="421">
@@ -12605,7 +12605,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I421" t="str">
-        <v>REM A19b | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
+        <v>REM A19b | SECCIÓN A: ATENCIÓN OFICINAS DE INFORMACIONES (SISTEMA INTEGRAL DE ATENCIÓN A USUARIOS) | Celdas (B11) debe ser igual a | celda (E11:I11)</v>
       </c>
     </row>
     <row r="422">
@@ -12808,7 +12808,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I428" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | celda (Y23:AA23)</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | celda (Y23:AA23)</v>
       </c>
     </row>
     <row r="429">
@@ -12837,7 +12837,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I429" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | celda (Y23:AA23)</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | celda (Y23:AA23)</v>
       </c>
     </row>
     <row r="430">
@@ -12866,7 +12866,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I430" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | celda (Y23:AA23)</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | celda (Y23:AA23)</v>
       </c>
     </row>
     <row r="431">
@@ -12895,7 +12895,7 @@
         <v>Omitida: v1 es 0</v>
       </c>
       <c r="I431" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | celda (Y23:AA23)</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | celda (Y23:AA23)</v>
       </c>
     </row>
     <row r="432">
@@ -12924,7 +12924,7 @@
         <v>Omitida: v1 es 0</v>
       </c>
       <c r="I432" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | celda (Y23:AA23)</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | celda (Y23:AA23)</v>
       </c>
     </row>
     <row r="433">
@@ -12953,7 +12953,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I433" t="str">
-        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | celda (Y23:AA23)</v>
+        <v>REM A27 | SECCIÓN A: PERSONAS QUE INGRESAN A EDUCACIÓN GRUPAL SEGÚN ÁREAS TEMÁTICAS Y EDAD | Celdas (D23) debe ser mayor o igual a | celda (Y23:AA23)</v>
       </c>
     </row>
     <row r="434">
@@ -12982,7 +12982,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I434" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
       </c>
     </row>
     <row r="435">
@@ -13011,7 +13011,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I435" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
       </c>
     </row>
     <row r="436">
@@ -13040,7 +13040,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I436" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
       </c>
     </row>
     <row r="437">
@@ -13069,7 +13069,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I437" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
       </c>
     </row>
     <row r="438">
@@ -13098,7 +13098,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I438" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
       </c>
     </row>
     <row r="439">
@@ -13127,7 +13127,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I439" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser menor o igual a | SECCIÓN A.3: EVALUACIÓN INICIAL | celda (B61)</v>
       </c>
     </row>
     <row r="440">
@@ -13156,7 +13156,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I440" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B14)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B14)</v>
       </c>
     </row>
     <row r="441">
@@ -13185,7 +13185,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I441" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B14)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B14)</v>
       </c>
     </row>
     <row r="442">
@@ -13214,7 +13214,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I442" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B14)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B14)</v>
       </c>
     </row>
     <row r="443">
@@ -13243,7 +13243,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I443" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B14)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B14)</v>
       </c>
     </row>
     <row r="444">
@@ -13272,7 +13272,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I444" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B14)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B14)</v>
       </c>
     </row>
     <row r="445">
@@ -13301,7 +13301,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I445" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B14)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B14)</v>
       </c>
     </row>
     <row r="446">
@@ -13330,7 +13330,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I446" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B15)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B15)</v>
       </c>
     </row>
     <row r="447">
@@ -13359,7 +13359,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I447" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B15)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B15)</v>
       </c>
     </row>
     <row r="448">
@@ -13388,7 +13388,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I448" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B15)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B15)</v>
       </c>
     </row>
     <row r="449">
@@ -13417,7 +13417,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I449" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B15)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B15)</v>
       </c>
     </row>
     <row r="450">
@@ -13446,7 +13446,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I450" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B15)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B15)</v>
       </c>
     </row>
     <row r="451">
@@ -13475,7 +13475,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I451" t="str">
-        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | SECCIÓN A.1: INGRESOS Y EGRESOS A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | celda (B15)</v>
+        <v>REM A28 | SECCIÓN A.1: INGRESOS Y EGRESOS  A ATENCIONES DE REHABILITACIÓN EN EL NIVEL PRIMARIO | Celdas (B13) debe ser mayor o igual a | celda (B15)</v>
       </c>
     </row>
     <row r="452">
@@ -13504,7 +13504,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I452" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | celda (B30:B52)</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | celda (B30:B52)</v>
       </c>
     </row>
     <row r="453">
@@ -13533,7 +13533,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I453" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | celda (B30:B52)</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | celda (B30:B52)</v>
       </c>
     </row>
     <row r="454">
@@ -13562,7 +13562,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I454" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | celda (B30:B52)</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | celda (B30:B52)</v>
       </c>
     </row>
     <row r="455">
@@ -13591,7 +13591,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I455" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | celda (B30:B52)</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | celda (B30:B52)</v>
       </c>
     </row>
     <row r="456">
@@ -13620,7 +13620,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I456" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | celda (B30:B52)</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | celda (B30:B52)</v>
       </c>
     </row>
     <row r="457">
@@ -13649,7 +13649,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I457" t="str">
-        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | celda (B30:B52)</v>
+        <v>REM A28 | SECCIÓN A.2: INGRESOS POR CONDICIÓN DE SALUD | Celdas (B29) debe ser menor o igual a | celda (B30:B52)</v>
       </c>
     </row>
     <row r="458">
@@ -13678,7 +13678,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I458" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | celda (B150:B177)</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | celda (B150:B177)</v>
       </c>
     </row>
     <row r="459">
@@ -13707,7 +13707,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I459" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | celda (B150:B177)</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | celda (B150:B177)</v>
       </c>
     </row>
     <row r="460">
@@ -13736,7 +13736,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I460" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | celda (B150:B177)</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | celda (B150:B177)</v>
       </c>
     </row>
     <row r="461">
@@ -13765,7 +13765,7 @@
         <v>Omitida: ambos 0</v>
       </c>
       <c r="I461" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | celda (B150:B177)</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | celda (B150:B177)</v>
       </c>
     </row>
     <row r="462">
@@ -13794,7 +13794,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I462" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | celda (B150:B177)</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | celda (B150:B177)</v>
       </c>
     </row>
     <row r="463">
@@ -13823,7 +13823,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I463" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | celda (B150:B177)</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (B149) debe ser menor o igual a | celda (B150:B177)</v>
       </c>
     </row>
     <row r="464">
@@ -13852,7 +13852,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I464" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es menor que 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser mayor o igual a | celda (0)</v>
       </c>
     </row>
     <row r="465">
@@ -13881,7 +13881,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I465" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es menor que 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser mayor o igual a | celda (0)</v>
       </c>
     </row>
     <row r="466">
@@ -13910,7 +13910,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I466" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es menor que 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser mayor o igual a | celda (0)</v>
       </c>
     </row>
     <row r="467">
@@ -13939,7 +13939,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I467" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es menor que 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser mayor o igual a | celda (0)</v>
       </c>
     </row>
     <row r="468">
@@ -13968,7 +13968,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I468" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es menor que 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser mayor o igual a | celda (0)</v>
       </c>
     </row>
     <row r="469">
@@ -13997,7 +13997,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I469" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es menor que 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser mayor o igual a | celda (0)</v>
       </c>
     </row>
     <row r="470">
@@ -14026,7 +14026,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I470" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es igual a 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="471">
@@ -14055,7 +14055,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I471" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es igual a 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="472">
@@ -14084,7 +14084,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I472" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es igual a 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="473">
@@ -14104,16 +14104,16 @@
         <v>0</v>
       </c>
       <c r="F473" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G473" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H473" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I473" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es igual a 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="474">
@@ -14133,16 +14133,16 @@
         <v>10</v>
       </c>
       <c r="F474" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G474" t="str">
         <v>Sí</v>
       </c>
       <c r="H474" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I474" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es igual a 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="475">
@@ -14171,7 +14171,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I475" t="str">
-        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS A REHABILITACIÓN INTEGRAL | La prestación 'TOTAL INGRESO (N° DE PERSONAS)' (AM149:AM177) es igual a 0</v>
+        <v>REM A28 | SECCIÓN B.1: INGRESOS Y EGRESOS  A REHABILITACIÓN INTEGRAL | Celdas (AM149:AM177) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="476">
@@ -14200,7 +14200,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I476" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Oftalmología/UAPO' (O12:P12) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (O12:P12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="477">
@@ -14229,7 +14229,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I477" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Oftalmología/UAPO' (O12:P12) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (O12:P12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="478">
@@ -14258,7 +14258,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I478" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Oftalmología/UAPO' (O12:P12) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (O12:P12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="479">
@@ -14278,16 +14278,16 @@
         <v>0</v>
       </c>
       <c r="F479" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G479" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H479" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I479" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Oftalmología/UAPO' (O12:P12) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (O12:P12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="480">
@@ -14307,16 +14307,16 @@
         <v>10</v>
       </c>
       <c r="F480" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G480" t="str">
         <v>Sí</v>
       </c>
       <c r="H480" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I480" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Oftalmología/UAPO' (O12:P12) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (O12:P12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="481">
@@ -14345,7 +14345,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I481" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Oftalmología/UAPO' (O12:P12) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (O12:P12) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="482">
@@ -14374,7 +14374,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I482" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Otorrinolaringología/UAPORRINO' (M13:N13) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (M13:N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="483">
@@ -14403,7 +14403,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I483" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Otorrinolaringología/UAPORRINO' (M13:N13) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (M13:N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="484">
@@ -14432,7 +14432,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I484" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Otorrinolaringología/UAPORRINO' (M13:N13) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (M13:N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="485">
@@ -14452,16 +14452,16 @@
         <v>0</v>
       </c>
       <c r="F485" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G485" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H485" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I485" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Otorrinolaringología/UAPORRINO' (M13:N13) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (M13:N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="486">
@@ -14481,16 +14481,16 @@
         <v>10</v>
       </c>
       <c r="F486" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G486" t="str">
         <v>Sí</v>
       </c>
       <c r="H486" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I486" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Otorrinolaringología/UAPORRINO' (M13:N13) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (M13:N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="487">
@@ -14519,7 +14519,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I487" t="str">
-        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | La prestación 'PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD Consultas médicas de especialidades Otorrinolaringología/UAPORRINO' (M13:N13) es igual a 0</v>
+        <v>REM A29 | SECCIÓN A: PROGRAMA DE RESOLUTIVIDAD ATENCIÓN PRIMARIA DE SALUD | Celdas (M13:N13) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="488">
@@ -14548,7 +14548,7 @@
         <v>Regla arroja ERROR</v>
       </c>
       <c r="I488" t="str">
-        <v>REM A30R | La prestación 'Descripción no encontrada' (B16:B17) es igual a 0</v>
+        <v>REM A30R |SECCION A1: TELEINTERCONSULTA DE ESPECIALIDAD MEDICA POR HOSPITAL DIGITAL Celdas (B16:B17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="489">
@@ -14577,7 +14577,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I489" t="str">
-        <v>REM A30R | La prestación 'Descripción no encontrada' (B16:B17) es igual a 0</v>
+        <v>REM A30R |SECCION A1: TELEINTERCONSULTA DE ESPECIALIDAD MEDICA POR HOSPITAL DIGITAL Celdas (B16:B17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="490">
@@ -14606,7 +14606,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I490" t="str">
-        <v>REM A30R | La prestación 'Descripción no encontrada' (B16:B17) es igual a 0</v>
+        <v>REM A30R |SECCION A1: TELEINTERCONSULTA DE ESPECIALIDAD MEDICA POR HOSPITAL DIGITAL Celdas (B16:B17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="491">
@@ -14626,16 +14626,16 @@
         <v>0</v>
       </c>
       <c r="F491" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G491" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="H491" t="str">
-        <v>Regla arroja ERROR</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I491" t="str">
-        <v>REM A30R | La prestación 'Descripción no encontrada' (B16:B17) es igual a 0</v>
+        <v>REM A30R |SECCION A1: TELEINTERCONSULTA DE ESPECIALIDAD MEDICA POR HOSPITAL DIGITAL Celdas (B16:B17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="492">
@@ -14655,16 +14655,16 @@
         <v>10</v>
       </c>
       <c r="F492" t="str">
-        <v>No</v>
+        <v>Sí</v>
       </c>
       <c r="G492" t="str">
         <v>Sí</v>
       </c>
       <c r="H492" t="str">
-        <v>Regla se cumple</v>
+        <v>Omitida: v1 es 0</v>
       </c>
       <c r="I492" t="str">
-        <v>REM A30R | La prestación 'Descripción no encontrada' (B16:B17) es igual a 0</v>
+        <v>REM A30R |SECCION A1: TELEINTERCONSULTA DE ESPECIALIDAD MEDICA POR HOSPITAL DIGITAL Celdas (B16:B17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
     <row r="493">
@@ -14693,7 +14693,7 @@
         <v>Regla se cumple</v>
       </c>
       <c r="I493" t="str">
-        <v>REM A30R | La prestación 'Descripción no encontrada' (B16:B17) es igual a 0</v>
+        <v>REM A30R |SECCION A1: TELEINTERCONSULTA DE ESPECIALIDAD MEDICA POR HOSPITAL DIGITAL Celdas (B16:B17) debe ser distinto de | celda (0)</v>
       </c>
     </row>
   </sheetData>
